--- a/docs/plan/TEA-PLAN-001_development-plan.xlsx
+++ b/docs/plan/TEA-PLAN-001_development-plan.xlsx
@@ -776,7 +776,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>84 across 7 families — all families accepted</t>
+          <t>85 across 7 families — all families accepted; one rule added post-review</t>
         </is>
       </c>
     </row>
@@ -1334,14 +1334,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Review scope — 84 review points in 7 families</t>
+          <t>Review scope — 85 review points in 7 families</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>All seven families accepted at the Step 1 review. Full catalog with logic and confidence base rates lives in TEA-SPEC-001.</t>
+          <t>All seven families accepted at the Step 1 review. TE-RS-021 added afterwards from the OI-01 discussion, off by default. Full catalog lives in TEA-SPEC-001.</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="C7" s="26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>All four response components versus derivation, nadir correctness, the 20%-plus-5mm rule, CR conditions including nodal short axis, unequivocal non-target progression, the overall response table, confirmation, best overall response, progression dating. These directly determine ORR, BOR, PFS and DoR.</t>
+          <t>All four response components versus derivation, nadir correctness, the 20%-plus-5mm rule, CR conditions including nodal short axis, unequivocal non-target progression, the overall response table, confirmation, best overall response, progression dating, and cytological confirmation of an effusion driving progression. These directly determine ORR, BOR, PFS and DoR.</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -6509,21 +6509,21 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>7 rule families, 84 review points</t>
+          <t>7 rule families, 85 review points</t>
         </is>
       </c>
       <c r="C13" s="16">
         <f>SUM(Review_Scope!C4:C10)</f>
         <v/>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>all accepted</t>
+          <t>TE-RS-021 added</t>
         </is>
       </c>
     </row>
@@ -6935,7 +6935,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Everything else is closed. These carry into Step 2.</t>
+          <t>OI-01 closed 2026-08-17. The remaining five carry into Step 2.</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>The OQ-05 indication roadmap lists 'pleural effusion' alongside prostate, colorectal, pancreatic, head and neck and ovarian cancer. Pleural effusion is a finding type, not an indication, and under RECIST it is non-measurable disease already handled by rule TE-BL-007. Confirm whether mesothelioma was intended, or whether the entry belongs to a different list.</t>
+          <t>CLOSED 2026-08-17. Mesothelioma was not intended. Pleural effusion is therefore not an indication and does not enter the roadmap. Reviewing what the entry was pointing at surfaced a genuine coverage gap: RECIST 1.1 requires cytological confirmation of an effusion appearing or worsening on treatment before it may be taken as progression, and no rule covered it. Added as TE-RS-021, PROPOSED_OPTIONAL — decision at the Step 2 gate under SQ-04.</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>Affects only the post-release roadmap, not release 1 scope. Left out of the roadmap until confirmed.</t>
+          <t>Effusions were already covered as non-measurable disease (TE-BL-007) and as a genuine case of unequivocal non-target progression (TE-RS-007). The unconfirmed-effusion pattern is a recognised source of spurious progression, which censors subjects early and shortens PFS.</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>Before roadmap planning</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>Confidence base rate per rule — 84 values to be assigned and agreed.</t>
+          <t>Confidence base rate per rule — 85 values to be assigned and agreed.</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">

--- a/docs/plan/TEA-PLAN-001_development-plan.xlsx
+++ b/docs/plan/TEA-PLAN-001_development-plan.xlsx
@@ -1,37 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Contents" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Objectives" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Scope" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Principles" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Components" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Confidence_Model" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Query_Handling" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="LLM_Policy" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Data_Model" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Review_Scope" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Architecture" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Web_App" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Delivery_Steps" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Requirements" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Risks" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Metrics" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Recommendations" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Decisions" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Open_Items" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Validation" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Version_Control" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Assumptions" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Glossary" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="References" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contents" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objectives" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Principles" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Components" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence_Model" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Handling" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Policy" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Scope" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_App" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery_Steps" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Items" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Version_Control" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objectives'!$A$3:$G$12</definedName>
@@ -1334,14 +1334,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Review scope — 85 review points in 7 families</t>
+          <t>Review scope — 85 review points in 7 families, 83 live</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>All seven families accepted at the Step 1 review. TE-RS-021 added afterwards from the OI-01 discussion, off by default. Full catalog lives in TEA-SPEC-001.</t>
+          <t>All seven families accepted at Step 1. At the Step 2 review all 85 rules were dispositioned over two rounds; TE-RS-010 and TE-RS-011 were retired, and their ids are retained permanently. Full catalog lives in TEA-SPEC-001.</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C4" s="28" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Rules complete</t>
         </is>
       </c>
       <c r="D4" s="23" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="F4" s="23" t="inlineStr">
         <is>
-          <t>Every review point reviewed and accepted, amended or removed; confidence base rate agreed per rule; rule pack frozen at 1.0.0.</t>
+          <t>RULES DONE — all 85 dispositioned over two rounds (2026-08-19, 2026-08-21); logic, severities and confidence base rates settled; 2 rules retired. REMAINING — Rule_Messages query wording, then the pack freezes.</t>
         </is>
       </c>
     </row>
@@ -6935,7 +6935,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>OI-01 closed 2026-08-17. The remaining five carry into Step 2.</t>
+          <t>OI-01 closed 2026-08-17, OI-02 closed 2026-08-21. Four remain.</t>
         </is>
       </c>
     </row>
@@ -7001,12 +7001,12 @@
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>Confidence base rate per rule — 85 values to be assigned and agreed.</t>
+          <t>CLOSED 2026-08-21. Confidence base rates were carried on every rule row and accepted with the rules across both Step 2 review rounds. Recorded as covered rather than separately signed off — SQ-02 on the specification's Open_Questions sheet remains available to correct any individual value.</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>Drives triage for every finding the agent ever produces. Proposed values are supplied in TEA-SPEC-001 for review rather than left blank.</t>
+          <t>Drives triage for every finding the agent produces. Range 0.30 to 0.97, mean 0.78.</t>
         </is>
       </c>
       <c r="D5" s="26" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>Step 2 gate</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>

--- a/docs/plan/TEA-PLAN-001_development-plan.xlsx
+++ b/docs/plan/TEA-PLAN-001_development-plan.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>TEA-SPEC-001 Programming Specification</t>
+          <t>TEA-SPEC-001 v2.0.0 — APPROVED 2026-08-21, rule pack frozen</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Step 2 — specification review and rule pack freeze</t>
+          <t>Step 3 — prototype output on a curated dummy dataset</t>
         </is>
       </c>
     </row>
@@ -2366,9 +2366,9 @@
           <t>Programming specification</t>
         </is>
       </c>
-      <c r="C4" s="28" t="inlineStr">
-        <is>
-          <t>Rules complete</t>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="D4" s="23" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="F4" s="23" t="inlineStr">
         <is>
-          <t>RULES DONE — all 85 dispositioned over two rounds (2026-08-19, 2026-08-21); logic, severities and confidence base rates settled; 2 rules retired. REMAINING — Rule_Messages query wording, then the pack freezes.</t>
+          <t>PASSED 2026-08-21. All 85 rules, all 85 query messages and all 9 open questions accepted over three review rounds; a reviewer-lens pass then changed 27 rules and was approved at the gate. Rule pack FROZEN at 2.0.0. Approved as a reasonableness review — see the specification's Approval sheet.</t>
         </is>
       </c>
     </row>
@@ -2396,9 +2396,9 @@
           <t>Prototype output on dummy data</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>NEXT</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">

--- a/docs/plan/TEA-PLAN-001_development-plan.xlsx
+++ b/docs/plan/TEA-PLAN-001_development-plan.xlsx
@@ -36,7 +36,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objectives'!$A$3:$G$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Requirements'!$A$3:$H$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Risks'!$A$3:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Risks'!$A$3:$I$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Decisions'!$A$3:$F$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -258,7 +258,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -271,7 +271,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -704,7 +704,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1.0.0</t>
+          <t>1.1.0</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>APPROVED — Step 1 gate passed</t>
+          <t>APPROVED — amended under change control 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>v0.1.0 draft (XML), issued 2026-08-10</t>
+          <t>v1.0.0, issued 2026-08-17</t>
         </is>
       </c>
     </row>
@@ -759,70 +759,82 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Indications, release 1</t>
+          <t>Language model</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>NSCLC and breast cancer</t>
+          <t>Company-hosted GLM v5.2 only. No external or commercial LLM service is used.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Review points</t>
+          <t>Indications, release 1</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>85 across 7 families — all families accepted; one rule added post-review</t>
+          <t>NSCLC and breast cancer</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Review disposition</t>
+          <t>Review points</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>95 items: 78 Accept, 3 Amend, 14 questions closed</t>
+          <t>85 across 7 families — all families accepted; one rule added post-review</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Reviewed by</t>
+          <t>Review disposition</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Daniel — 2026-08-17</t>
+          <t>95 items: 78 Accept, 3 Amend, 14 questions closed</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Child document</t>
+          <t>Reviewed by</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>TEA-SPEC-001 v2.0.0 — APPROVED 2026-08-21, rule pack frozen</t>
+          <t>Daniel — 2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>Child document</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>TEA-SPEC-001 v2.0.0 — APPROVED 2026-08-21, rule pack frozen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>Next gate</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Step 3 — prototype output on a curated dummy dataset</t>
         </is>
@@ -831,96 +843,109 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>WHAT CHANGED AT THIS REVISION</t>
+          <t>WHAT CHANGED AT v1.1.0 — SINGLE-MODEL AMENDMENT</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Unaffected by this amendment. Still FROZEN at 2.0.0.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>•  OBJ-03 amended — every finding now carries a confidence rate (xx.x%) expressing how likely it is to be a correct query. See the Confidence_Model sheet.</t>
+          <t>•  The agent now runs on the company-hosted GLM v5.2 and nothing else. Commercial and externally hosted LLM services are out of scope, not merely deprioritised.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>•  OBJ-04 amended — the agent now assesses whether a site's answer to a past query was reasonable, instead of re-raising whenever data still fails.</t>
+          <t>•  Deployment mode A (cloud-assisted) is removed. Two modes remain: GLM v5.2 on-premise, and deterministic-only.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>•  OBJ-06 amended — RECIST 1.0 removed from scope. Guideline packs are RECIST 1.1 and iRECIST only.</t>
+          <t>•  Provider adapters reduce from four to two — GLM v5.2, and the null adapter that runs deterministic-only.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>•  Data source settled — Veeva EDC export is the primary profile, with a structured CRF specification supplied. SDTM becomes secondary.</t>
+          <t>•  REG-07 no longer gates release: no subject data reaches an external model because there is no external model. The privacy assessment becomes a record, not a blocker.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>•  New capability — protocol intake assistant (AC-11): the agent summarises protocol parameter checkpoints for the user to confirm before the first run.</t>
+          <t>•  RSK-04 (data leaving the boundary) drops to negligible. RSK-16 is added in its place: with one model there is no second provider to fall back to.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>•  Release 1 simplifications — no strict role separation; on-demand runs only; English only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1"/>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+          <t>•  Cross-provider conformance testing is replaced, not deleted. See the note below — this matters more than it looks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>•  The rule pack is untouched. No rule references a provider, so the 2.0.0 freeze holds and no rule change control is triggered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1"/>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>HOW TO USE THIS WORKBOOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>•  Yellow cells are for reviewers. Every other cell is controlled content — please do not overwrite it.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>•  Decisions recorded at the Step 1 review are preserved on each register sheet in the Decision / Reviewer / Comment columns.</t>
+          <t>•  Yellow cells are for reviewers. Every other cell is controlled content — please do not overwrite it.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>•  Open_Items lists what is still outstanding after this review. Everything else is closed.</t>
+          <t>•  Decisions recorded at the Step 1 review are preserved on each register sheet in the Decision / Reviewer / Comment columns.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
+          <t>•  Open_Items lists what is still outstanding after this review. Everything else is closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
           <t>•  Contents tracks item counts and remaining decisions with live formulas.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="28">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="B18:F18"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A23:F23"/>
@@ -933,10 +958,12 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B19:F19"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="A24:F24"/>
+    <mergeCell ref="B20:F20"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="A4:F5"/>
     <mergeCell ref="A25:F25"/>
@@ -1665,7 +1692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1908,12 +1935,12 @@
       </c>
       <c r="B19" s="26" t="inlineStr">
         <is>
-          <t>Internal gateway with per-provider adapters</t>
+          <t>Company-hosted GLM v5.2 via the internal gateway</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>Central place for redaction, rate limiting, logging and model pinning.</t>
+          <t>One model. The gateway remains the place for rate limiting, logging and version pinning; redaction is much lighter now that nothing leaves the network.</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1957,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Required for the local-LLM, no-external-egress configuration (OQ-10).</t>
+          <t>No external egress at all. This is now the only configuration, not one option among several.</t>
         </is>
       </c>
     </row>
@@ -1966,12 +1993,12 @@
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>Cloud-assisted</t>
+          <t>On-premise with GLM v5.2</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Commercial LLM API. Requires an approved data transfer path and de-identification. Not used until the privacy assessment completes (OQ-10).</t>
+          <t>The steady-state and only production mode. GLM v5.2 served internally; no subject data leaves the network.</t>
         </is>
       </c>
     </row>
@@ -1983,29 +2010,12 @@
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>On-premise with local LLM</t>
+          <t>Deterministic-only</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>GLM served internally; no subject data leaves the network. Expected steady-state mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t>Deterministic-only</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>No LLM. Rule coverage intact, template narratives, and confidence falls back to the rule base rate alone.</t>
+          <t>No model at all. Full rule coverage, template narratives, and confidence from the rule base rate and evidence completeness alone. Runs in CI on every commit as the verdict reference, and is the operating mode if GLM is unavailable.</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2483,7 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>All rules implemented with tests; golden dataset regression green; catalog drift check green; conformance suite green across providers.</t>
+          <t>All rules implemented with tests; golden dataset regression green; catalog drift check green; verdict identity green between GLM v5.2 and deterministic-only.</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2870,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Run with any configured LLM provider, including a local GLM deployment, and in deterministic-only mode.</t>
+          <t>Run against the company-hosted GLM v5.2, and in deterministic-only mode. The model adapter stays behind an interface so a future model change is an adapter, not a rewrite.</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
@@ -2868,9 +2878,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>CARRIED</t>
+      <c r="F10" s="27" t="inlineStr">
+        <is>
+          <t>AMENDED</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr">
@@ -3241,7 +3251,7 @@
           <t>Support incremental runs processing only data changed since the previous snapshot. Deferred beyond release 1 — runs are on-demand (OQ-12).</t>
         </is>
       </c>
-      <c r="E19" s="29" t="inlineStr">
+      <c r="E19" s="34" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
@@ -3283,7 +3293,7 @@
           <t>Allow reviewer-authored suppression rules for known-acceptable patterns, with expiry and audit.</t>
         </is>
       </c>
-      <c r="E20" s="34" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
@@ -3448,7 +3458,7 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Given the same input snapshot, configuration and versions, deterministic findings are identical across runs and across LLM providers.</t>
+          <t>Given the same input snapshot, configuration and versions, deterministic findings are identical across runs, and identical whether GLM v5.2 is used or the deterministic-only mode is.</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
@@ -3456,9 +3466,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>CARRIED</t>
+      <c r="F24" s="27" t="inlineStr">
+        <is>
+          <t>AMENDED</t>
         </is>
       </c>
       <c r="G24" s="18" t="inlineStr">
@@ -3616,7 +3626,7 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>No single LLM call exceeds a 32k-token prompt budget, so smaller local models remain viable.</t>
+          <t>No single model call exceeds the prompt budget confirmed against the GLM v5.2 deployment. The 32k assumption from OQ-03 is carried forward as a working figure and must be verified, not assumed.</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -3624,9 +3634,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
-        <is>
-          <t>CARRIED</t>
+      <c r="F28" s="27" t="inlineStr">
+        <is>
+          <t>AMENDED</t>
         </is>
       </c>
       <c r="G28" s="18" t="inlineStr">
@@ -3658,7 +3668,7 @@
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>Subject data encrypted at rest and in transit; egress policy enforced by configuration. Release 1 does not enforce role separation (OQ-08).</t>
+          <t>Subject data encrypted at rest and in transit, and never leaves the company network — there is no external model call to make. Release 1 does not enforce role separation (OQ-08).</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -3871,7 +3881,7 @@
           <t>English only in release 1; templates structured to allow localisation later (OQ-11).</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
+      <c r="E34" s="29" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
@@ -4162,7 +4172,7 @@
       </c>
       <c r="D41" s="23" t="inlineStr">
         <is>
-          <t>Data privacy assessment completed before any subject data reaches an external model; on-premise or deterministic-only until it is.</t>
+          <t>No subject data reaches an external model, because no external model is used. The privacy assessment records the on-premise architecture rather than gating release, as it did at v1.0.0.</t>
         </is>
       </c>
       <c r="E41" s="24" t="inlineStr">
@@ -4170,9 +4180,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="F41" s="25" t="inlineStr">
-        <is>
-          <t>CARRIED</t>
+      <c r="F41" s="28" t="inlineStr">
+        <is>
+          <t>AMENDED</t>
         </is>
       </c>
       <c r="G41" s="22" t="inlineStr">
@@ -4202,7 +4212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4429,9 +4439,9 @@
           <t>Data privacy</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
@@ -4446,12 +4456,12 @@
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>Egress policy enforced in configuration; de-identification layer; on-premise GLM as steady-state; deterministic-only mode available.</t>
+          <t>Structurally removed at v1.1.0: there is no external model adapter to call. The only paths are the internal GLM v5.2 gateway and deterministic-only.</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
         <is>
-          <t>Low once the privacy assessment under REG-07 is complete.</t>
+          <t>Negligible. The risk is now a deployment-configuration error rather than a design exposure.</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -4661,7 +4671,7 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>Model portability</t>
+          <t>Model capability</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
@@ -4676,17 +4686,17 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>A local GLM deployment lacks reliable structured output or tool calling, producing malformed responses.</t>
+          <t>GLM v5.2 lacks reliable structured output, or its context limit is smaller than the 32k assumed at OQ-03, producing malformed or truncated responses.</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Capability matrix per adapter; schema validation with bounded repair; deterministic template fallback; conformance suite run per provider before use.</t>
+          <t>Capability confirmed against the actual v5.2 deployment before Step 5 rather than assumed; schema validation with bounded repair; deterministic template fallback on every LLM task.</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Low — worst case is degraded narrative quality, never a wrong verdict.</t>
+          <t>Low — worst case is degraded narrative quality, never a wrong verdict. But the capability check is now a real task, not a formality.</t>
         </is>
       </c>
       <c r="H12" s="18" t="inlineStr">
@@ -4982,8 +4992,55 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>RSK-16</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Single-model dependency</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>With one model there is no second provider to fall back to. If GLM v5.2 is retired, upgraded in place, or unavailable for a period, there is no alternative that produces comparable narrative quality.</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>The deterministic-only mode keeps the system fully operational with template narratives and base-rate confidence, so a model outage degrades output rather than stopping review. The adapter interface is retained so a future model is an adapter rather than a rewrite. Model version is pinned per study and recorded in provenance, so an in-place upgrade is detected rather than silently changing narratives.</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>Moderate. Accepted deliberately in exchange for removing the external-egress exposure entirely.</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:I18"/>
+  <autoFilter ref="A3:I19"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -5218,32 +5275,32 @@
     <row r="9">
       <c r="A9" s="36" t="inlineStr">
         <is>
-          <t>Provider verdict identity</t>
+          <t>Verdict identity</t>
         </is>
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>Deterministic verdicts identical across providers</t>
+          <t>Deterministic verdicts identical between a GLM v5.2 run and a deterministic-only run of the same snapshot</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>1.00, enforced by CI</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="inlineStr">
-        <is>
-          <t>CARRIED</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>Accept</t>
+          <t>1.00, enforced by CI on every commit</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>AMENDED</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="26" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5734,7 @@
           <t>REC-10</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5850,19 +5907,19 @@
           <t>LLM deployment</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
-        <is>
-          <t>Assumption accepted</t>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>Answered v1.1.0</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>OpenAI-compatible gateway with JSON mode, no reliable constrained decoding; 32k prompt budget with schema validation and repair.</t>
+          <t>Company-hosted GLM v5.2, and nothing else. The v1.0.0 assumption (OpenAI-compatible gateway, JSON mode, 32k budget) is carried forward as a working figure only — it was never verified against v5.2 and must be before Step 5.</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Adapter strategy and NFR-05 stand as drafted.</t>
+          <t>Adapters reduce to two. NFR-05 amended to make the budget a figure to confirm rather than a stated fact.</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -5978,7 +6035,7 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Assumption accepted</t>
         </is>
@@ -6042,7 +6099,7 @@
           <t>Acceptance thresholds</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Assumption accepted</t>
         </is>
@@ -6074,19 +6131,19 @@
           <t>Data privacy</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
-        <is>
-          <t>Assumption accepted</t>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Answered v1.1.0</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>On-premise or deterministic-only until a privacy assessment completes.</t>
+          <t>On-premise only, permanently. Cloud-assisted operation is out of scope rather than deferred.</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t>Deployment mode A unavailable at release. REG-07 stands.</t>
+          <t>Deployment mode A removed entirely. REG-07 becomes a record rather than a release gate.</t>
         </is>
       </c>
       <c r="F13" s="26" t="inlineStr">
@@ -6170,7 +6227,7 @@
           <t>Independent central review</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Assumption accepted</t>
         </is>
@@ -6202,7 +6259,7 @@
           <t>Validation expectations</t>
         </is>
       </c>
-      <c r="C17" s="29" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>Assumption accepted</t>
         </is>
@@ -6636,7 +6693,7 @@
         </is>
       </c>
       <c r="C18" s="16">
-        <f>COUNTA(Risks!A4:A18)</f>
+        <f>COUNTA(Risks!A4:A19)</f>
         <v/>
       </c>
       <c r="D18" s="17" t="inlineStr">
@@ -6935,7 +6992,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>OI-01 closed 2026-08-17, OI-02 closed 2026-08-21. Four remain.</t>
+          <t>OI-01, OI-02 and OI-06 closed. Three remain — OI-03 (pilot study) is the one blocking Step 3.</t>
         </is>
       </c>
     </row>
@@ -7109,12 +7166,12 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>Privacy assessment enabling deployment mode A, if cloud-assisted operation is ever wanted.</t>
+          <t>CLOSED 2026-08-22. Superseded by the single-model amendment: deployment mode A is removed and cloud-assisted operation is out of scope, so there is no external model call for a privacy assessment to gate. The assessment becomes a record of the on-premise architecture, owned by IT security, with no dependency on it.</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>Not blocking: modes B and C cover release 1.</t>
+          <t>Was the last privacy-related blocker. Removing the external model removed the exposure rather than mitigating it.</t>
         </is>
       </c>
       <c r="D9" s="26" t="inlineStr">
@@ -7124,7 +7181,7 @@
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -7239,88 +7296,100 @@
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>Provider conformance testing</t>
+          <t>Verdict identity testing</t>
         </is>
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>The same fixture set through every configured LLM provider. Deterministic verdicts must be identical; narrative outputs scored against a rubric.</t>
+          <t>AMENDED at v1.1.0. With one model, comparing providers no longer proves anything, so the comparison moves to GLM v5.2 against the deterministic-only reference. Deterministic verdicts must be identical between the two; only narrative and adjudication may differ. This is what still guarantees the model cannot change a verdict.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>User acceptance testing</t>
+          <t>GLM capability verification</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Reviewers run realistic tasks on a de-identified real study, against criteria agreed at the Step 3 gate.</t>
+          <t>Confirm the v5.2 deployment against what the adapter assumes — structured output support, context limit, latency under load — before Step 5 rather than discovering it during implementation.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>Installation and operational qualification</t>
+          <t>User acceptance testing</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>Environment, configuration, access, backup and audit trail verification, scaled per deployment mode.</t>
+          <t>Reviewers run realistic tasks on a de-identified real study, against criteria agreed at the Step 3 gate.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
+          <t>Installation and operational qualification</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Environment, configuration, access, backup and audit trail verification, scaled per deployment mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
           <t>Periodic review</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>Rule pack effectiveness reviewed per data cut using disposition statistics; model and prompt versions re-verified when changed.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Reference frameworks</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>•  ISPE GAMP 5 (2nd edition) risk-based approach to compliant GxP computerized systems.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>•  FDA guidance on Computer Software Assurance for production and quality system software.</t>
+          <t>•  ISPE GAMP 5 (2nd edition) risk-based approach to compliant GxP computerized systems.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>•  21 CFR Part 11 and EU GMP Annex 11 — audit trail, access control, records.</t>
+          <t>•  FDA guidance on Computer Software Assurance for production and quality system software.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>•  ICH E6(R3) Good Clinical Practice.</t>
+          <t>•  21 CFR Part 11 and EU GMP Annex 11 — audit trail, access control, records.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>•  ICH E6(R3) Good Clinical Practice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>•  ALCOA+ data integrity principles.</t>
         </is>
@@ -8185,7 +8254,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Run against a commercial LLM API and a company-hosted local LLM (GLM family) with identical review verdicts and no code changes beyond configuration.</t>
+          <t>Run entirely on the company-hosted GLM v5.2, with no dependency on any external or commercial LLM service. Deterministic verdicts must be identical whether the model is available or not, which the deterministic-only mode exists to prove.</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
@@ -8193,14 +8262,14 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>CARRIED</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>Accept</t>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>AMENDED</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>Amend</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -8208,7 +8277,11 @@
           <t>Daniel</t>
         </is>
       </c>
-      <c r="G8" s="12" t="n"/>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Consider GLM v5.2 working and exclude other commercialized LLM. Focusing on the internal company GLM.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
@@ -8362,7 +8435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8630,12 +8703,12 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>Languages other than English.</t>
+          <t>Commercial and externally hosted LLM services. The agent uses the company-hosted GLM v5.2 only, and no subject data leaves the network.</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>OQ-11</t>
+          <t>OBJ-05 amended v1.1.0</t>
         </is>
       </c>
     </row>
@@ -8647,12 +8720,12 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Non-solid-tumor criteria (Lugano, IMWG, PCWG3, RANO) and modality variants (mRECIST, Choi).</t>
+          <t>Languages other than English.</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>OQ-06</t>
+          <t>OQ-11</t>
         </is>
       </c>
     </row>
@@ -8664,12 +8737,12 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>Endpoint derivation for submission, which remains owned by biostatistics.</t>
+          <t>Non-solid-tumor criteria (Lugano, IMWG, PCWG3, RANO) and modality variants (mRECIST, Choi).</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>Carried</t>
+          <t>OQ-06</t>
         </is>
       </c>
     </row>
@@ -8681,27 +8754,44 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
+          <t>Endpoint derivation for submission, which remains owned by biostatistics.</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Carried</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>Out of scope</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
           <t>Medical decision-making. The agent produces suspicions for human adjudication.</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>REG-01</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>Roadmap</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Further indications after release 1: prostate, colorectal, pancreatic, head and neck, ovarian cancer.</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>OQ-05</t>
         </is>
@@ -8767,7 +8857,7 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Every numeric derivation and rule verdict is computed by rule-pack code. The LLM may only adjudicate rules declared judgement-based, assess free text, explain, and draft language. This keeps verdicts identical when moving between a commercial API and a local GLM deployment.</t>
+          <t>Every numeric derivation and rule verdict is computed by rule-pack code. The LLM may only adjudicate rules declared judgement-based, assess free text, explain, and draft language. Verdicts are therefore identical whether GLM v5.2 answers, returns nonsense, or is switched off entirely.</t>
         </is>
       </c>
     </row>
@@ -9704,7 +9794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9716,7 +9806,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>LLM usage policy and provider adapters</t>
+          <t>LLM usage policy and model adapters</t>
         </is>
       </c>
     </row>
@@ -9933,7 +10023,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Provider adapters</t>
+          <t>Model adapters — one model, plus the deterministic-only reference (v1.1.0)</t>
         </is>
       </c>
     </row>
@@ -9962,88 +10052,44 @@
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>Anthropic Claude API</t>
+          <t>GLM v5.2 (company-hosted)</t>
         </is>
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>Native SDK</t>
+          <t>Internal gateway</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Tool-use / JSON schema</t>
+          <t>To be confirmed against the deployment</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Reference implementation.</t>
+          <t>The only model adapter. Transport, structured-output support and context limit are configuration confirmed against the actual v5.2 deployment at Step 5, not assumed here.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="22" t="inlineStr">
         <is>
-          <t>OpenAI-compatible</t>
+          <t>Null / deterministic-only</t>
         </is>
       </c>
       <c r="B21" s="26" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>JSON schema, prompt fallback</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>Covers GLM via an OpenAI-compatible gateway, vLLM, SGLang, Ollama. Assumption accepted at OQ-03.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>GLM native</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>JSON mode + prompt fallback</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Separate adapter: parameter naming and tool-call semantics differ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="22" t="inlineStr">
-        <is>
-          <t>Null</t>
-        </is>
-      </c>
-      <c r="B23" s="26" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D23" s="23" t="inlineStr">
-        <is>
-          <t>Deterministic-only mode; every LLM task falls back to its template.</t>
+          <t>Not a fallback of last resort but the reference implementation: it defines the verdicts GLM must not change. Every conformance run compares GLM output against it.</t>
         </is>
       </c>
     </row>

--- a/docs/plan/TEA-PLAN-001_development-plan.xlsx
+++ b/docs/plan/TEA-PLAN-001_development-plan.xlsx
@@ -35,7 +35,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objectives'!$A$3:$G$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Requirements'!$A$3:$H$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Requirements'!$A$3:$H$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Risks'!$A$3:$I$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Decisions'!$A$3:$F$17</definedName>
   </definedNames>
@@ -704,7 +704,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.2.0</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>v1.0.0, issued 2026-08-17</t>
+          <t>v1.1.0, issued 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3443,22 +3443,22 @@
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>NFR-01</t>
+          <t>FR-21</t>
         </is>
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Reproducibility</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Given the same input snapshot, configuration and versions, deterministic findings are identical across runs, and identical whether GLM v5.2 is used or the deterministic-only mode is.</t>
+          <t>Record for every protocol parameter whether it was found in the source document, with its location, or defaulted because it was not found — and show the two differently at the intake screen. A defaulted parameter is the one a reviewer most needs to see.</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
@@ -3466,9 +3466,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="F24" s="27" t="inlineStr">
-        <is>
-          <t>AMENDED</t>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>NEW v1.2.0</t>
         </is>
       </c>
       <c r="G24" s="18" t="inlineStr">
@@ -3485,7 +3485,7 @@
     <row r="25">
       <c r="A25" s="22" t="inlineStr">
         <is>
-          <t>NFR-02</t>
+          <t>NFR-01</t>
         </is>
       </c>
       <c r="B25" s="26" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Maintainability</t>
+          <t>Reproducibility</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>Adding a review point requires only a new rule module, its fixtures and a catalog entry. Verified by a CI check.</t>
+          <t>Given the same input snapshot, configuration and versions, deterministic findings are identical across runs, and identical whether GLM v5.2 is used or the deterministic-only mode is.</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -3508,9 +3508,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="F25" s="25" t="inlineStr">
-        <is>
-          <t>CARRIED</t>
+      <c r="F25" s="28" t="inlineStr">
+        <is>
+          <t>AMENDED</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -3527,7 +3527,7 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>NFR-03</t>
+          <t>NFR-02</t>
         </is>
       </c>
       <c r="B26" s="21" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Maintainability</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>500 subjects with 12 assessments each complete a deterministic full run in under 5 minutes on standard hardware.</t>
+          <t>Adding a review point requires only a new rule module, its fixtures and a catalog entry. Verified by a CI check.</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
@@ -3569,7 +3569,7 @@
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>NFR-04</t>
+          <t>NFR-03</t>
         </is>
       </c>
       <c r="B27" s="26" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>Web application list views respond within 2 seconds at 10,000 findings.</t>
-        </is>
-      </c>
-      <c r="E27" s="28" t="inlineStr">
-        <is>
-          <t>Should</t>
+          <t>500 subjects with 12 assessments each complete a deterministic full run in under 5 minutes on standard hardware.</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>Must</t>
         </is>
       </c>
       <c r="F27" s="25" t="inlineStr">
@@ -3611,7 +3611,7 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>NFR-05</t>
+          <t>NFR-04</t>
         </is>
       </c>
       <c r="B28" s="21" t="inlineStr">
@@ -3621,22 +3621,22 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Portability</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>No single model call exceeds the prompt budget confirmed against the GLM v5.2 deployment. The 32k assumption from OQ-03 is carried forward as a working figure and must be verified, not assumed.</t>
-        </is>
-      </c>
-      <c r="E28" s="19" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="inlineStr">
-        <is>
-          <t>AMENDED</t>
+          <t>Web application list views respond within 2 seconds at 10,000 findings.</t>
+        </is>
+      </c>
+      <c r="E28" s="27" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>CARRIED</t>
         </is>
       </c>
       <c r="G28" s="18" t="inlineStr">
@@ -3653,7 +3653,7 @@
     <row r="29">
       <c r="A29" s="22" t="inlineStr">
         <is>
-          <t>NFR-06</t>
+          <t>NFR-05</t>
         </is>
       </c>
       <c r="B29" s="26" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Portability</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>Subject data encrypted at rest and in transit, and never leaves the company network — there is no external model call to make. Release 1 does not enforce role separation (OQ-08).</t>
+          <t>No single model call exceeds the prompt budget confirmed against the GLM v5.2 deployment. The 32k assumption from OQ-03 is carried forward as a working figure and must be verified, not assumed.</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -3695,7 +3695,7 @@
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>NFR-07</t>
+          <t>NFR-06</t>
         </is>
       </c>
       <c r="B30" s="21" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Audit trail meeting ALCOA+ expectations on all human actions and agent runs; records retained per sponsor policy.</t>
+          <t>Subject data encrypted at rest and in transit, and never leaves the company network — there is no external model call to make. Release 1 does not enforce role separation (OQ-08).</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
@@ -3718,9 +3718,9 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="F30" s="20" t="inlineStr">
-        <is>
-          <t>CARRIED</t>
+      <c r="F30" s="27" t="inlineStr">
+        <is>
+          <t>AMENDED</t>
         </is>
       </c>
       <c r="G30" s="18" t="inlineStr">
@@ -3737,7 +3737,7 @@
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>NFR-08</t>
+          <t>NFR-07</t>
         </is>
       </c>
       <c r="B31" s="26" t="inlineStr">
@@ -3747,17 +3747,17 @@
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>Usability</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>A reviewer can go from a finding to full context and back in a single click, with no loss of filter state.</t>
-        </is>
-      </c>
-      <c r="E31" s="28" t="inlineStr">
-        <is>
-          <t>Should</t>
+          <t>Audit trail meeting ALCOA+ expectations on all human actions and agent runs; records retained per sponsor policy.</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>Must</t>
         </is>
       </c>
       <c r="F31" s="25" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>NFR-09</t>
+          <t>NFR-08</t>
         </is>
       </c>
       <c r="B32" s="21" t="inlineStr">
@@ -3789,17 +3789,17 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>Usability</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>An LLM outage degrades the system to deterministic-only mode rather than failing the run.</t>
-        </is>
-      </c>
-      <c r="E32" s="19" t="inlineStr">
-        <is>
-          <t>Must</t>
+          <t>A reviewer can go from a finding to full context and back in a single click, with no loss of filter state.</t>
+        </is>
+      </c>
+      <c r="E32" s="27" t="inlineStr">
+        <is>
+          <t>Should</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -3821,7 +3821,7 @@
     <row r="33">
       <c r="A33" s="22" t="inlineStr">
         <is>
-          <t>NFR-10</t>
+          <t>NFR-09</t>
         </is>
       </c>
       <c r="B33" s="26" t="inlineStr">
@@ -3831,22 +3831,22 @@
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>Observability</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>Every run emits metrics: rule hit counts, adjudication rates, confidence calibration, model latency, disposition outcomes.</t>
-        </is>
-      </c>
-      <c r="E33" s="28" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="F33" s="28" t="inlineStr">
-        <is>
-          <t>AMENDED</t>
+          <t>An LLM outage degrades the system to deterministic-only mode rather than failing the run.</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="F33" s="25" t="inlineStr">
+        <is>
+          <t>CARRIED</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
@@ -3863,7 +3863,7 @@
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>NFR-11</t>
+          <t>NFR-10</t>
         </is>
       </c>
       <c r="B34" s="21" t="inlineStr">
@@ -3873,17 +3873,17 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Internationalisation</t>
+          <t>Observability</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>English only in release 1; templates structured to allow localisation later (OQ-11).</t>
-        </is>
-      </c>
-      <c r="E34" s="29" t="inlineStr">
-        <is>
-          <t>Could</t>
+          <t>Every run emits metrics: rule hit counts, adjudication rates, confidence calibration, model latency, disposition outcomes.</t>
+        </is>
+      </c>
+      <c r="E34" s="27" t="inlineStr">
+        <is>
+          <t>Should</t>
         </is>
       </c>
       <c r="F34" s="27" t="inlineStr">
@@ -3905,32 +3905,32 @@
     <row r="35">
       <c r="A35" s="22" t="inlineStr">
         <is>
-          <t>REG-01</t>
+          <t>NFR-11</t>
         </is>
       </c>
       <c r="B35" s="26" t="inlineStr">
         <is>
-          <t>Regulatory</t>
+          <t>Non-functional</t>
         </is>
       </c>
       <c r="C35" s="26" t="inlineStr">
         <is>
-          <t>Intended use</t>
+          <t>Internationalisation</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>The system is decision support; a qualified human makes every determination and issues every query manually.</t>
-        </is>
-      </c>
-      <c r="E35" s="24" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="F35" s="25" t="inlineStr">
-        <is>
-          <t>CARRIED</t>
+          <t>English only in release 1; templates structured to allow localisation later (OQ-11).</t>
+        </is>
+      </c>
+      <c r="E35" s="34" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="F35" s="28" t="inlineStr">
+        <is>
+          <t>AMENDED</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -3947,7 +3947,7 @@
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>REG-02</t>
+          <t>REG-01</t>
         </is>
       </c>
       <c r="B36" s="21" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Intended use</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Risk-based validation consistent with GAMP 5 (2nd ed.) and the FDA Computer Software Assurance approach.</t>
+          <t>The system is decision support; a qualified human makes every determination and issues every query manually.</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr">
@@ -3989,7 +3989,7 @@
     <row r="37">
       <c r="A37" s="22" t="inlineStr">
         <is>
-          <t>REG-03</t>
+          <t>REG-02</t>
         </is>
       </c>
       <c r="B37" s="26" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="C37" s="26" t="inlineStr">
         <is>
-          <t>Records</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>Where used in a GxP process, 21 CFR Part 11 and EU Annex 11 expectations apply to audit trail, access control and record retention.</t>
+          <t>Risk-based validation consistent with GAMP 5 (2nd ed.) and the FDA Computer Software Assurance approach.</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
@@ -4031,7 +4031,7 @@
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>REG-04</t>
+          <t>REG-03</t>
         </is>
       </c>
       <c r="B38" s="21" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>Traceability</t>
+          <t>Records</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Specification-to-test traceability: every requirement and every rule traces to at least one test case.</t>
+          <t>Where used in a GxP process, 21 CFR Part 11 and EU Annex 11 expectations apply to audit trail, access control and record retention.</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr">
@@ -4073,7 +4073,7 @@
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>REG-05</t>
+          <t>REG-04</t>
         </is>
       </c>
       <c r="B39" s="26" t="inlineStr">
@@ -4083,12 +4083,12 @@
       </c>
       <c r="C39" s="26" t="inlineStr">
         <is>
-          <t>Change control</t>
+          <t>Traceability</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
         <is>
-          <t>Rule pack and prompt changes follow documented review and approval, with impact assessment on previously issued findings.</t>
+          <t>Specification-to-test traceability: every requirement and every rule traces to at least one test case.</t>
         </is>
       </c>
       <c r="E39" s="24" t="inlineStr">
@@ -4115,7 +4115,7 @@
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>REG-06</t>
+          <t>REG-05</t>
         </is>
       </c>
       <c r="B40" s="21" t="inlineStr">
@@ -4125,17 +4125,17 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>GCP</t>
+          <t>Change control</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Alignment with ICH E6(R3) expectations on risk-proportionate, quality-by-design monitoring approaches.</t>
-        </is>
-      </c>
-      <c r="E40" s="27" t="inlineStr">
-        <is>
-          <t>Should</t>
+          <t>Rule pack and prompt changes follow documented review and approval, with impact assessment on previously issued findings.</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>Must</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
@@ -4157,47 +4157,89 @@
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
         <is>
+          <t>REG-06</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>Alignment with ICH E6(R3) expectations on risk-proportionate, quality-by-design monitoring approaches.</t>
+        </is>
+      </c>
+      <c r="E41" s="28" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="F41" s="25" t="inlineStr">
+        <is>
+          <t>CARRIED</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="H41" s="26" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
           <t>REG-07</t>
         </is>
       </c>
-      <c r="B41" s="26" t="inlineStr">
+      <c r="B42" s="21" t="inlineStr">
         <is>
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C41" s="26" t="inlineStr">
+      <c r="C42" s="21" t="inlineStr">
         <is>
           <t>Privacy</t>
         </is>
       </c>
-      <c r="D41" s="23" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>No subject data reaches an external model, because no external model is used. The privacy assessment records the on-premise architecture rather than gating release, as it did at v1.0.0.</t>
         </is>
       </c>
-      <c r="E41" s="24" t="inlineStr">
+      <c r="E42" s="19" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="F41" s="28" t="inlineStr">
+      <c r="F42" s="27" t="inlineStr">
         <is>
           <t>AMENDED</t>
         </is>
       </c>
-      <c r="G41" s="22" t="inlineStr">
+      <c r="G42" s="18" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
       </c>
-      <c r="H41" s="26" t="inlineStr">
+      <c r="H42" s="21" t="inlineStr">
         <is>
           <t>Daniel</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H41"/>
+  <autoFilter ref="A3:H42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
@@ -6663,11 +6705,11 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>20 functional, 11 non-functional, 7 regulatory</t>
+          <t>21 functional, 11 non-functional, 7 regulatory</t>
         </is>
       </c>
       <c r="C17" s="16">
-        <f>COUNTA(Requirements!A4:A41)</f>
+        <f>COUNTA(Requirements!A4:A42)</f>
         <v/>
       </c>
       <c r="D17" s="17" t="inlineStr">
@@ -6992,7 +7034,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>OI-01, OI-02 and OI-06 closed. Three remain — OI-03 (pilot study) is the one blocking Step 3.</t>
+          <t>OI-01, OI-02 and OI-06 closed. Three remain — OI-05 is the one blocking Step 3, not OI-03.</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7186,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Entry criterion for Step 2. The mapping profile cannot be built without it.</t>
+          <t>ESCALATED v1.2.0. This was an entry criterion for Step 2 and was never delivered — Step 2 closed on the strength of the rule review alone. It is now the real blocker for Step 3: the synthetic dataset has to be shaped like an actual CRF, and TE-BL-011 and TE-FU-001 are CONDITIONAL on whether the sum is site-entered, which cannot be settled for a real study without the CRF specification.</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -7154,7 +7196,7 @@
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>Step 2 start</t>
+          <t>BLOCKING Step 3</t>
         </is>
       </c>
     </row>

--- a/docs/plan/TEA-PLAN-001_development-plan.xlsx
+++ b/docs/plan/TEA-PLAN-001_development-plan.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1.2.0</t>
+          <t>1.3.0</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>v1.1.0, issued 2026-08-22</t>
+          <t>v1.2.0, issued 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -5097,7 +5097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5118,7 +5118,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Targets accepted at review (OQ-09). Calibration error added with the confidence rate.</t>
+          <t>AMENDED v1.3.0. These are the stated expectation, not yet the agreed acceptance criteria — those are settled after the Step 3 prototype output is seen. See the note below the table.</t>
         </is>
       </c>
     </row>
@@ -5410,10 +5410,82 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>How these numbers get settled — decision of 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>The acceptance thresholds are confirmed after the Step 3 prototype output has been seen, rather than fixed now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>Why that is reasonable</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Several of these numbers cannot be guessed honestly in advance. Nobody knows what precision an 83-rule pack achieves on this data until it runs, and a threshold invented at the desk is no more defensible than one set from evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>What it costs, stated plainly</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>A threshold set after seeing the result is fitted to the result. It stops being a test the system can fail and becomes a description of how the system behaved. That matters here because these numbers end up in the validation package as acceptance criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>So the safeguard</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>The targets in the table above stay on record as the expectation held BEFORE the run. Step 3 records what was actually observed alongside them. Moving a target then requires a written reason — why the original expectation was wrong, not merely that it was not met. The number that reaches the validation package is then a decision with a rationale rather than a restatement of the outcome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>Who decides</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>CDM lead and Medical Monitor jointly, the same pair who sign off the expected finding list (OQ-09).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6141,19 +6213,19 @@
           <t>Acceptance thresholds</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
-        <is>
-          <t>Assumption accepted</t>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>Answered v1.3.0</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Targets as drafted; golden dataset signed off jointly by CDM lead and Medical Monitor.</t>
+          <t>CDM and the Medical Monitor sign off the expected finding list on the golden dataset. The acceptance thresholds themselves are confirmed after the Step 3 output has been seen, not before.</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Metrics sheet stands, with calibration error added.</t>
+          <t>Metrics sheet becomes a stated expectation rather than agreed criteria; moving a target after the run requires a written reason. See the note under the Metrics table.</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -6839,7 +6911,7 @@
         </is>
       </c>
       <c r="C22" s="16">
-        <f>COUNTA(Open_Items!A4:A9)</f>
+        <f>COUNTA(Open_Items!A4:A10)</f>
         <v/>
       </c>
       <c r="D22" s="14" t="inlineStr">
@@ -7014,7 +7086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7034,7 +7106,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>OI-01, OI-02 and OI-06 closed. Three remain — OI-05 is the one blocking Step 3, not OI-03.</t>
+          <t>OI-01, OI-02 and OI-06 closed. Four remain — OI-05 is the one blocking Step 3, not OI-03.</t>
         </is>
       </c>
     </row>
@@ -7224,6 +7296,33 @@
       <c r="E9" s="26" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>OI-07</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Content selection rule for the protocol summary — which sections the study data manager extracts, agreed with the Medical Monitor. The parameter list P1 to P18 on the specification's GLM_Verification sheet is the proposed basis.</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>The summary is now an input to the system, so what goes into it determines what the agent can know. Agreeing it once as a rule is what stops it being re-decided per study by whoever happens to prepare it.</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>CDM + Medical Monitor</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>Before Step 3 output is reviewed</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9215,7 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>NEW at review. Reads the protocol and imaging charter, summarises every parameter the rule pack depends on — confirmation requirement, assessment interval and window, minimum SD duration, iRECIST confirmation window, marker usage, target lesion limits — and presents them as checkpoints for the user to confirm or correct before the first run. Output is the signed-off protocol configuration.</t>
+          <t>AMENDED v1.3.0. Reads a protocol summary prepared beforehand by the study data manager against a content selection rule agreed with the Medical Monitor — not the full protocol. Summarises every parameter the rule pack depends on — confirmation requirement, assessment interval and window, minimum SD duration, iRECIST confirmation window, marker usage, target lesion limits — and presents them as checkpoints for the user to confirm or correct before the first run, each marked as found in the summary or defaulted because it was absent (FR-21). Output is the signed-off protocol configuration.</t>
         </is>
       </c>
     </row>

--- a/docs/plan/TEA-PLAN-001_development-plan.xlsx
+++ b/docs/plan/TEA-PLAN-001_development-plan.xlsx
@@ -36,7 +36,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objectives'!$A$3:$G$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Requirements'!$A$3:$H$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Risks'!$A$3:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Risks'!$A$3:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Decisions'!$A$3:$F$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -704,7 +704,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1.3.0</t>
+          <t>1.4.0</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>v1.2.0, issued 2026-08-22</t>
+          <t>v1.3.0, issued 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5081,8 +5081,102 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>RSK-17</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Derived input</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>SDTM is a derived representation, not source data. If the EDC-to-SDTM conversion is wrong, the agent reviews the conversion's errors rather than the site's — and raises queries about mapping bugs, which is the fastest way to lose a data manager's trust.</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Conformance-check every incoming dataset against the input contract before any rule runs, and treat a conformance failure as a run-blocking defect rather than a finding. The ST family already catches part of this — referential integrity, duplicate identity, unit consistency — but it was written for EDC extracts, not for conversion output, and should be re-read with that in mind at Step 3.</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Moderate. Falls as the conversion matures, and is much lower if the mapping is executed by reviewed deterministic code rather than generated per-record.</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>RSK-18</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>LLM-generated input</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>Using an LLM to convert EDC data into SDTM would place the model upstream of every verdict. DP-01 exists to stop exactly that: verdicts are reproducible because no model touches the data they are computed from. A model that builds the input can invent a value, and the deterministic rules would then faithfully check the invention. Volume makes it worse — tens of thousands of rows per study — and NFR-01 reproducibility cannot hold across runs.</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>The model writes the mapping SPECIFICATION and drafts the mapping CODE; a human reviews both; deterministic code executes the mapping every time. That is the same split DP-01 already applies to review, applied to conversion. A conversion is a transformation, not a judgement, so nothing is lost by making it deterministic.</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>Low if the split is kept. The risk is entirely in the choice of pattern, not in the technology.</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="I21" s="26" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:I19"/>
+  <autoFilter ref="A3:I21"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -5957,19 +6051,19 @@
           <t>Data source</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>Answered</t>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>REVERSED v1.4.0</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Veeva EDC export, with the CRF specification supplied as structured data.</t>
+          <t>SDTM becomes the primary input; the Veeva EDC export is no longer read directly by the agent. The v1.0.0 answer rested on the CRF specification being supplied as structured data, and it cannot be — so the reasoning behind it no longer holds. SDTM is standardised, publicly documented, and can be built against outside the company.</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Veeva becomes the primary ingestion profile; SDTM demoted to secondary. The mapping configuration is largely generated from the CRF specification rather than hand-written.</t>
+          <t>Ingestion targets SDTM TU, TR and RS plus the standard cross-domain domains. The adapter interface is kept, so a direct Veeva reader remains addable later without touching the rules.</t>
         </is>
       </c>
       <c r="F4" s="21" t="inlineStr">
@@ -6807,7 +6901,7 @@
         </is>
       </c>
       <c r="C18" s="16">
-        <f>COUNTA(Risks!A4:A19)</f>
+        <f>COUNTA(Risks!A4:A21)</f>
         <v/>
       </c>
       <c r="D18" s="17" t="inlineStr">
@@ -6911,7 +7005,7 @@
         </is>
       </c>
       <c r="C22" s="16">
-        <f>COUNTA(Open_Items!A4:A10)</f>
+        <f>COUNTA(Open_Items!A4:A12)</f>
         <v/>
       </c>
       <c r="D22" s="14" t="inlineStr">
@@ -7086,7 +7180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7106,7 +7200,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>OI-01, OI-02 and OI-06 closed. Four remain — OI-05 is the one blocking Step 3, not OI-03.</t>
+          <t>OI-01, OI-02, OI-05 and OI-06 closed. Five remain. Nothing now blocks Step 3 — OI-08 is the next thing to do, not a thing to wait for.</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7352,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>ESCALATED v1.2.0. This was an entry criterion for Step 2 and was never delivered — Step 2 closed on the strength of the rule review alone. It is now the real blocker for Step 3: the synthetic dataset has to be shaped like an actual CRF, and TE-BL-011 and TE-FU-001 are CONDITIONAL on whether the sum is site-entered, which cannot be settled for a real study without the CRF specification.</t>
+          <t>CLOSED v1.4.0 — superseded, not delivered. The raw export and CRF specification cannot be released, so the input moves to SDTM, which is standardised and can be built against outside the company. This unblocks Step 3 rather than deferring it. TE-BL-011 and TE-FU-001 stay CONDITIONAL, now resolved against the SDTM contract instead of a CRF specification.</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -7268,7 +7362,7 @@
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>BLOCKING Step 3</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -7323,6 +7417,60 @@
       <c r="E10" s="21" t="inlineStr">
         <is>
           <t>Before Step 3 output is reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>OI-08</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>SDTM input contract: which domains, which variables, which are required, and what the agent does when an optional one is absent. Needed BEFORE the dummy data is built, not after — it is the contract the dummy data and the later conversion both target.</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>Without it the dummy data is shaped by guesswork and the definition step just documents whatever emerged. TU, TR and RS carry the tumor data; DM, EX, AE, DS, CM and PR cover the cross-domain rules. Two gaps need a decision: query history has no SDTM home, and imaging metadata is not standard.</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>Clinical programming</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>Before dummy data is built</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>OI-09</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Supplementary query-history input. SDTM has no query domain, so the query-management family and the whole of AC-06 have no data to work from unless a separate extract accompanies the SDTM. A small flat file is enough: query id, subject, form, field, text, answer, status, dates.</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>5 rules and the entire query reconciliation model depend on it. Without it the agent re-raises every finding at every data cut, which is the behaviour OBJ-04 was written to prevent.</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>Clinical programming</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>With OI-08</t>
         </is>
       </c>
     </row>

--- a/docs/plan/TEA-PLAN-001_development-plan.xlsx
+++ b/docs/plan/TEA-PLAN-001_development-plan.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1.4.0</t>
+          <t>1.5.0</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>v1.3.0, issued 2026-08-22</t>
+          <t>v1.4.0, issued 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -7428,12 +7428,12 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>SDTM input contract: which domains, which variables, which are required, and what the agent does when an optional one is absent. Needed BEFORE the dummy data is built, not after — it is the contract the dummy data and the later conversion both target.</t>
+          <t>SDTM input contract: which domains, which variables, which are required, and what the agent does when an optional one is absent.</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>Without it the dummy data is shaped by guesswork and the definition step just documents whatever emerged. TU, TR and RS carry the tumor data; DM, EX, AE, DS, CM and PR cover the cross-domain rules. Two gaps need a decision: query history has no SDTM home, and imaging metadata is not standard.</t>
+          <t>DRAFTED 2026-08-22 as TEA-CTR-003, on the specification's SDTM_Requirements sheet — 42 variables across 10 SDTM domains plus 3 supplementary inputs, derived from what the 83 live rules consume, with 10 conversion traps. Needs review, then it becomes the target for both the dummy data and the later conversion.</t>
         </is>
       </c>
       <c r="D11" s="26" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>Before dummy data is built</t>
+          <t>Review before dummy data is built</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Supplementary query-history input. SDTM has no query domain, so the query-management family and the whole of AC-06 have no data to work from unless a separate extract accompanies the SDTM. A small flat file is enough: query id, subject, form, field, text, answer, status, dates.</t>
+          <t>Supplementary query-history input. Specified on the SDTM_Requirements sheet as the QUERY* row, marked required.</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>5 rules and the entire query reconciliation model depend on it. Without it the agent re-raises every finding at every data cut, which is the behaviour OBJ-04 was written to prevent.</t>
+          <t>5 rules and the entire query reconciliation model depend on it. Without it the agent re-raises every finding at every data cut, which is the behaviour OBJ-04 was written to prevent. It is the largest single gap in an SDTM-only delivery.</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>With OI-08</t>
+          <t>Confirm it can be extracted from Veeva</t>
         </is>
       </c>
     </row>
